--- a/老虎机数学入门-PartIV-WayGame模型.xlsx
+++ b/老虎机数学入门-PartIV-WayGame模型.xlsx
@@ -8572,6 +8572,9 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:BF292" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20985,5 +20988,8 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:BS131" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>